--- a/data/summarized fitur Numeric - KBMI 4.xlsx
+++ b/data/summarized fitur Numeric - KBMI 4.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I89"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,6 +478,11 @@
           <t>total_npl_dan_restruk_npl</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>total_kredit_yang_diberikan</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -517,6 +522,7 @@
       <c r="I2" t="n">
         <v>9246283</v>
       </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -556,6 +562,7 @@
       <c r="I3" t="n">
         <v>18974721</v>
       </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -595,6 +602,7 @@
       <c r="I4" t="n">
         <v>9468447</v>
       </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -634,6 +642,7 @@
       <c r="I5" t="n">
         <v>25183949</v>
       </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -673,6 +682,9 @@
       <c r="I6" t="n">
         <v>7876926</v>
       </c>
+      <c r="J6" t="n">
+        <v>588250950</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -712,6 +724,9 @@
       <c r="I7" t="n">
         <v>18839262</v>
       </c>
+      <c r="J7" t="n">
+        <v>792351117</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -751,6 +766,9 @@
       <c r="I8" t="n">
         <v>11287990</v>
       </c>
+      <c r="J8" t="n">
+        <v>522750099</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -790,6 +808,9 @@
       <c r="I9" t="n">
         <v>22533385</v>
       </c>
+      <c r="J9" t="n">
+        <v>859570852</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -829,6 +850,7 @@
       <c r="I10" t="n">
         <v>9591304</v>
       </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -868,6 +890,7 @@
       <c r="I11" t="n">
         <v>18750859</v>
       </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -907,6 +930,7 @@
       <c r="I12" t="n">
         <v>12961718</v>
       </c>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -946,6 +970,7 @@
       <c r="I13" t="n">
         <v>24884232</v>
       </c>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -985,6 +1010,7 @@
       <c r="I14" t="n">
         <v>12134853</v>
       </c>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1024,6 +1050,7 @@
       <c r="I15" t="n">
         <v>25608898</v>
       </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1063,6 +1090,7 @@
       <c r="I16" t="n">
         <v>16489983</v>
       </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1102,6 +1130,7 @@
       <c r="I17" t="n">
         <v>25880579</v>
       </c>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1141,6 +1170,9 @@
       <c r="I18" t="n">
         <v>11010009</v>
       </c>
+      <c r="J18" t="n">
+        <v>569164386</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1180,6 +1212,9 @@
       <c r="I19" t="n">
         <v>26069798</v>
       </c>
+      <c r="J19" t="n">
+        <v>751156414</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1219,6 +1254,9 @@
       <c r="I20" t="n">
         <v>19538835</v>
       </c>
+      <c r="J20" t="n">
+        <v>548613540</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1258,6 +1296,9 @@
       <c r="I21" t="n">
         <v>26535025</v>
       </c>
+      <c r="J21" t="n">
+        <v>877560684</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1297,6 +1338,9 @@
       <c r="I22" t="n">
         <v>10326712</v>
       </c>
+      <c r="J22" t="n">
+        <v>575648735</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1336,6 +1380,9 @@
       <c r="I23" t="n">
         <v>24855920</v>
       </c>
+      <c r="J23" t="n">
+        <v>763603416</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1375,6 +1422,9 @@
       <c r="I24" t="n">
         <v>23467860</v>
       </c>
+      <c r="J24" t="n">
+        <v>551786774</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1414,6 +1464,9 @@
       <c r="I25" t="n">
         <v>25860442</v>
       </c>
+      <c r="J25" t="n">
+        <v>880685363</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1453,6 +1506,9 @@
       <c r="I26" t="n">
         <v>10507107</v>
       </c>
+      <c r="J26" t="n">
+        <v>573933771</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1492,6 +1548,9 @@
       <c r="I27" t="n">
         <v>25431703</v>
       </c>
+      <c r="J27" t="n">
+        <v>778954674</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1531,6 +1590,9 @@
       <c r="I28" t="n">
         <v>23003086</v>
       </c>
+      <c r="J28" t="n">
+        <v>558070101</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -1570,6 +1632,9 @@
       <c r="I29" t="n">
         <v>27986115</v>
       </c>
+      <c r="J29" t="n">
+        <v>896526155</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1609,6 +1674,9 @@
       <c r="I30" t="n">
         <v>13848933</v>
       </c>
+      <c r="J30" t="n">
+        <v>579912255</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -1648,6 +1716,9 @@
       <c r="I31" t="n">
         <v>25353306</v>
       </c>
+      <c r="J31" t="n">
+        <v>805204153</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -1687,6 +1758,9 @@
       <c r="I32" t="n">
         <v>22414340</v>
       </c>
+      <c r="J32" t="n">
+        <v>568536688</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -1726,6 +1800,9 @@
       <c r="I33" t="n">
         <v>29816440</v>
       </c>
+      <c r="J33" t="n">
+        <v>912082842</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -1765,6 +1842,9 @@
       <c r="I34" t="n">
         <v>13965569</v>
       </c>
+      <c r="J34" t="n">
+        <v>591363643</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -1804,6 +1884,9 @@
       <c r="I35" t="n">
         <v>24583573</v>
       </c>
+      <c r="J35" t="n">
+        <v>808863845</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -1843,6 +1926,9 @@
       <c r="I36" t="n">
         <v>21709846</v>
       </c>
+      <c r="J36" t="n">
+        <v>569568199</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -1882,6 +1968,9 @@
       <c r="I37" t="n">
         <v>30634892</v>
       </c>
+      <c r="J37" t="n">
+        <v>931051034</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -1921,6 +2010,9 @@
       <c r="I38" t="n">
         <v>13411713</v>
       </c>
+      <c r="J38" t="n">
+        <v>620640134</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -1960,6 +2052,9 @@
       <c r="I39" t="n">
         <v>23118893</v>
       </c>
+      <c r="J39" t="n">
+        <v>828113863</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -1999,6 +2094,9 @@
       <c r="I40" t="n">
         <v>21516016</v>
       </c>
+      <c r="J40" t="n">
+        <v>581497289</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -2038,6 +2136,9 @@
       <c r="I41" t="n">
         <v>29089725</v>
       </c>
+      <c r="J41" t="n">
+        <v>943702693</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -2077,6 +2178,9 @@
       <c r="I42" t="n">
         <v>14272446</v>
       </c>
+      <c r="J42" t="n">
+        <v>619851707</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -2116,6 +2220,9 @@
       <c r="I43" t="n">
         <v>22911721</v>
       </c>
+      <c r="J43" t="n">
+        <v>842354021</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -2155,6 +2262,9 @@
       <c r="I44" t="n">
         <v>20456435</v>
       </c>
+      <c r="J44" t="n">
+        <v>590845696</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -2194,6 +2304,9 @@
       <c r="I45" t="n">
         <v>30737634</v>
       </c>
+      <c r="J45" t="n">
+        <v>974801659</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -2233,6 +2346,9 @@
       <c r="I46" t="n">
         <v>14499204</v>
       </c>
+      <c r="J46" t="n">
+        <v>656872451</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -2272,6 +2388,9 @@
       <c r="I47" t="n">
         <v>21781754</v>
       </c>
+      <c r="J47" t="n">
+        <v>891122770</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -2311,6 +2430,9 @@
       <c r="I48" t="n">
         <v>19467481</v>
       </c>
+      <c r="J48" t="n">
+        <v>616605643</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -2350,6 +2472,9 @@
       <c r="I49" t="n">
         <v>33346801</v>
       </c>
+      <c r="J49" t="n">
+        <v>1003615576</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -2389,6 +2514,9 @@
       <c r="I50" t="n">
         <v>14324611</v>
       </c>
+      <c r="J50" t="n">
+        <v>662674349</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -2428,6 +2556,9 @@
       <c r="I51" t="n">
         <v>20361337</v>
       </c>
+      <c r="J51" t="n">
+        <v>907790606</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -2467,6 +2598,9 @@
       <c r="I52" t="n">
         <v>18835609</v>
       </c>
+      <c r="J52" t="n">
+        <v>619029583</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -2506,6 +2640,9 @@
       <c r="I53" t="n">
         <v>31601185</v>
       </c>
+      <c r="J53" t="n">
+        <v>1007118308</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -2545,6 +2682,9 @@
       <c r="I54" t="n">
         <v>11795528</v>
       </c>
+      <c r="J54" t="n">
+        <v>691141340</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -2584,6 +2724,9 @@
       <c r="I55" t="n">
         <v>17443643</v>
       </c>
+      <c r="J55" t="n">
+        <v>932639051</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -2623,6 +2766,9 @@
       <c r="I56" t="n">
         <v>18031393</v>
       </c>
+      <c r="J56" t="n">
+        <v>642629631</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -2662,6 +2808,9 @@
       <c r="I57" t="n">
         <v>29011509</v>
       </c>
+      <c r="J57" t="n">
+        <v>1029802549</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -2701,6 +2850,9 @@
       <c r="I58" t="n">
         <v>12189179</v>
       </c>
+      <c r="J58" t="n">
+        <v>693664500</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -2740,6 +2892,9 @@
       <c r="I59" t="n">
         <v>15647030</v>
       </c>
+      <c r="J59" t="n">
+        <v>927191716</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -2779,6 +2934,9 @@
       <c r="I60" t="n">
         <v>17448696</v>
       </c>
+      <c r="J60" t="n">
+        <v>629787384</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -2818,6 +2976,9 @@
       <c r="I61" t="n">
         <v>32127021</v>
       </c>
+      <c r="J61" t="n">
+        <v>1065324679</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -2857,6 +3018,9 @@
       <c r="I62" t="n">
         <v>13473376</v>
       </c>
+      <c r="J62" t="n">
+        <v>714633822</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -2896,6 +3060,9 @@
       <c r="I63" t="n">
         <v>14944030</v>
       </c>
+      <c r="J63" t="n">
+        <v>984680624</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -2935,6 +3102,9 @@
       <c r="I64" t="n">
         <v>15820369</v>
       </c>
+      <c r="J64" t="n">
+        <v>645510839</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -2974,6 +3144,9 @@
       <c r="I65" t="n">
         <v>33805511</v>
       </c>
+      <c r="J65" t="n">
+        <v>1089371656</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -3013,6 +3186,9 @@
       <c r="I66" t="n">
         <v>15168375</v>
       </c>
+      <c r="J66" t="n">
+        <v>743845569</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -3052,6 +3228,9 @@
       <c r="I67" t="n">
         <v>13752246</v>
       </c>
+      <c r="J67" t="n">
+        <v>1016043397</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -3091,6 +3270,9 @@
       <c r="I68" t="n">
         <v>15091155</v>
       </c>
+      <c r="J68" t="n">
+        <v>665138580</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -3130,6 +3312,9 @@
       <c r="I69" t="n">
         <v>36656304</v>
       </c>
+      <c r="J69" t="n">
+        <v>1136001212</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -3169,6 +3354,9 @@
       <c r="I70" t="n">
         <v>14147246</v>
       </c>
+      <c r="J70" t="n">
+        <v>787499389</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -3208,6 +3396,9 @@
       <c r="I71" t="n">
         <v>10999537</v>
       </c>
+      <c r="J71" t="n">
+        <v>1085787427</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -3247,6 +3438,9 @@
       <c r="I72" t="n">
         <v>14709637</v>
       </c>
+      <c r="J72" t="n">
+        <v>687912534</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -3286,6 +3480,9 @@
       <c r="I73" t="n">
         <v>35773138</v>
       </c>
+      <c r="J73" t="n">
+        <v>1146082506</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -3325,6 +3522,9 @@
       <c r="I74" t="n">
         <v>15249667</v>
       </c>
+      <c r="J74" t="n">
+        <v>811553747</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -3364,6 +3564,9 @@
       <c r="I75" t="n">
         <v>11269806</v>
       </c>
+      <c r="J75" t="n">
+        <v>1113886426</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -3403,6 +3606,9 @@
       <c r="I76" t="n">
         <v>13959859</v>
       </c>
+      <c r="J76" t="n">
+        <v>685956480</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -3442,6 +3648,9 @@
       <c r="I77" t="n">
         <v>38584747</v>
       </c>
+      <c r="J77" t="n">
+        <v>1181606235</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -3481,6 +3690,9 @@
       <c r="I78" t="n">
         <v>17627641</v>
       </c>
+      <c r="J78" t="n">
+        <v>824590282</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -3520,6 +3732,9 @@
       <c r="I79" t="n">
         <v>12041766</v>
       </c>
+      <c r="J79" t="n">
+        <v>1196095333</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -3559,6 +3774,9 @@
       <c r="I80" t="n">
         <v>14163207</v>
       </c>
+      <c r="J80" t="n">
+        <v>715466427</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -3598,6 +3816,9 @@
       <c r="I81" t="n">
         <v>38737339</v>
       </c>
+      <c r="J81" t="n">
+        <v>1207046873</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -3637,6 +3858,9 @@
       <c r="I82" t="n">
         <v>17485690</v>
       </c>
+      <c r="J82" t="n">
+        <v>851044543</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -3676,6 +3900,9 @@
       <c r="I83" t="n">
         <v>12008515</v>
       </c>
+      <c r="J83" t="n">
+        <v>1240837941</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -3715,6 +3942,9 @@
       <c r="I84" t="n">
         <v>14243640</v>
       </c>
+      <c r="J84" t="n">
+        <v>721758930</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -3754,6 +3984,9 @@
       <c r="I85" t="n">
         <v>36982789</v>
       </c>
+      <c r="J85" t="n">
+        <v>1216402988</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -3793,6 +4026,9 @@
       <c r="I86" t="n">
         <v>15498016</v>
       </c>
+      <c r="J86" t="n">
+        <v>894912082</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -3832,6 +4068,9 @@
       <c r="I87" t="n">
         <v>12609239</v>
       </c>
+      <c r="J87" t="n">
+        <v>1310779402</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -3871,6 +4110,9 @@
       <c r="I88" t="n">
         <v>14985219</v>
       </c>
+      <c r="J88" t="n">
+        <v>761550303</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -3909,6 +4151,9 @@
       </c>
       <c r="I89" t="n">
         <v>35681873</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1215847233</v>
       </c>
     </row>
   </sheetData>
